--- a/Luban/Datas/BossPhasePattern.xlsx
+++ b/Luban/Datas/BossPhasePattern.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -1524,102 +1524,6 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>boss_phase_pattern_boss_level1_enemy_08_phase_01_01</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>boss_level1_enemy_08_phase_01</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>level1_midboss_center_random_line@3+0.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>boss_phase_pattern_boss_level1_enemy_08_phase_01_02</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>boss_level1_enemy_08_phase_01</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>level1_midboss_windmill_cw@4+0.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>boss_phase_pattern_boss_level1_enemy_08_phase_01_03</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>boss_level1_enemy_08_phase_01</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>level1_midboss_windmill_ccw@4+2.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>boss_phase_pattern_boss_level1_enemy_08_phase_01_04</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>boss_level1_enemy_08_phase_01</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>level1_midboss_missile_pair@6+1.2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Datas/BossPhasePattern.xlsx
+++ b/Luban/Datas/BossPhasePattern.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>boss_p1_fan_09</t>
+          <t>boss_p1_fan_dense_5@1.15+0.2</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>boss_p1_sweep_single</t>
+          <t>boss_p1_slow_homing_5@5+1.8</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>boss_p2_ring_20</t>
+          <t>boss_p2_s_windmill_dense@1+0.2</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>boss_p2_aim_03</t>
+          <t>boss_p2_lock_dash_5@5+1.5</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>boss_p3_rotating_11</t>
+          <t>boss_p3_s_windmill_dense_big@0.8+0.1</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>boss_p3_aim_05</t>
+          <t>boss_p3_split_5@3+1.0</t>
         </is>
       </c>
     </row>

--- a/Luban/Datas/BossPhasePattern.xlsx
+++ b/Luban/Datas/BossPhasePattern.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPhasePattern" sheetId="1" r:id="R7f234dbf48e0496d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPhasePattern" sheetId="1" r:id="Ra7b7e113b7924339"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1461,7 +1461,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F45" t="str">
-        <x:v>boss_02_p1_center_ring_5@4+0.2</x:v>
+        <x:v>boss_02_p1_center_ring_3@2+0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -1479,7 +1479,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F46" t="str">
-        <x:v>boss_02_p1_side_homing_3@2+0.8</x:v>
+        <x:v>boss_02_p1_side_homing_1@2+0.8</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -1515,7 +1515,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F48" t="str">
-        <x:v>boss_02_p2_side_lock_2@1+0.6</x:v>
+        <x:v>boss_02_p2_side_fast_homing@1+0.6</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -1533,7 +1533,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F49" t="str">
-        <x:v>boss_02_p3_all_yellow_laser</x:v>
+        <x:v>boss_02_p3_side_laser@5+0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -1542,7 +1542,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C50" t="str">
-        <x:v>boss_phase_pattern_boss_02_phase_03_ring</x:v>
+        <x:v>boss_phase_pattern_boss_02_phase_03_homing</x:v>
       </x:c>
       <x:c r="D50" t="str">
         <x:v>boss_02_phase_03</x:v>
@@ -1551,44 +1551,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F50" t="str">
-        <x:v>boss_02_p3_all_ring</x:v>
+        <x:v>boss_02_p3_center_homing_burst@3+3.6</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51"/>
-      <x:c r="B51" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C51" t="str">
-        <x:v>boss_phase_pattern_boss_02_phase_03_homing</x:v>
-      </x:c>
-      <x:c r="D51" t="str">
-        <x:v>boss_02_phase_03</x:v>
-      </x:c>
-      <x:c r="E51" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F51" t="str">
-        <x:v>boss_02_p3_all_fast_homing</x:v>
-      </x:c>
+      <x:c r="B51"/>
+      <x:c r="C51"/>
+      <x:c r="D51"/>
+      <x:c r="E51"/>
+      <x:c r="F51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52"/>
-      <x:c r="B52" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C52" t="str">
-        <x:v>boss_phase_pattern_boss_02_phase_03_lock</x:v>
-      </x:c>
-      <x:c r="D52" t="str">
-        <x:v>boss_02_phase_03</x:v>
-      </x:c>
-      <x:c r="E52" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F52" t="str">
-        <x:v>boss_02_p3_all_fast_lock</x:v>
-      </x:c>
+      <x:c r="B52"/>
+      <x:c r="C52"/>
+      <x:c r="D52"/>
+      <x:c r="E52"/>
+      <x:c r="F52"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
